--- a/users.xlsx
+++ b/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEPCO_\Desktop\25보강공사\RPA\AMISAFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEPCO_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6135ED14-FBD7-432B-A24F-0A7B52E0395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FE4F21-D208-4926-98EB-4A1700109995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1800" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="2835" windowWidth="15180" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -67,9 +67,6 @@
     <t>홍길동</t>
   </si>
   <si>
-    <t>A조</t>
-  </si>
-  <si>
     <t>작업원</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
   </si>
   <si>
     <t>최민호</t>
-  </si>
-  <si>
-    <t>B조</t>
   </si>
   <si>
     <t>leader02</t>
@@ -133,10 +127,6 @@
   </si>
   <si>
     <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C조</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -554,13 +544,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -588,17 +578,17 @@
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>11</v>
@@ -607,25 +597,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>1111</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -634,25 +624,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2">
         <v>1111</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
@@ -661,25 +651,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2">
         <v>1111</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>11</v>
@@ -688,25 +678,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>1111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>11</v>
@@ -715,25 +705,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
         <v>1111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D8" s="2">
+        <v>6</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>11</v>
@@ -742,28 +732,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2">
         <v>1234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="D9" s="2">
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEPCO_\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEPCO_\Desktop\25보강공사\RPA\AMISAFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FE4F21-D208-4926-98EB-4A1700109995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6135ED14-FBD7-432B-A24F-0A7B52E0395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9960" yWindow="2835" windowWidth="15180" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="1800" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -67,6 +67,9 @@
     <t>홍길동</t>
   </si>
   <si>
+    <t>A조</t>
+  </si>
+  <si>
     <t>작업원</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
   </si>
   <si>
     <t>최민호</t>
+  </si>
+  <si>
+    <t>B조</t>
   </si>
   <si>
     <t>leader02</t>
@@ -127,6 +133,10 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C조</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -544,13 +554,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -578,17 +588,17 @@
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2">
-        <v>1</v>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>11</v>
@@ -597,25 +607,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <v>1111</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -624,25 +634,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
         <v>1111</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2">
-        <v>3</v>
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
@@ -651,25 +661,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2">
         <v>1111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>11</v>
@@ -678,25 +688,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2">
         <v>1111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2">
-        <v>5</v>
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>11</v>
@@ -705,25 +715,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2">
         <v>1111</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2">
-        <v>6</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>11</v>
@@ -732,28 +742,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2">
         <v>1234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="2">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEPCO_\Desktop\25보강공사\RPA\AMISAFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6135ED14-FBD7-432B-A24F-0A7B52E0395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3BEAC9-BCE9-4656-B2C5-76B2911E1F78}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1800" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21495" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -67,9 +67,6 @@
     <t>홍길동</t>
   </si>
   <si>
-    <t>A조</t>
-  </si>
-  <si>
     <t>작업원</t>
   </si>
   <si>
@@ -103,21 +100,10 @@
     <t>최민호</t>
   </si>
   <si>
-    <t>B조</t>
-  </si>
-  <si>
     <t>leader02</t>
   </si>
   <si>
     <t>정우성</t>
-  </si>
-  <si>
-    <t>본사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>kdncnami1!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>신하이</t>
@@ -136,7 +122,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C조</t>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -220,9 +214,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -260,9 +254,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -295,9 +289,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -330,9 +341,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,15 +581,13 @@
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
+      <c r="B2" s="2">
+        <v>1111</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
@@ -589,16 +615,16 @@
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>11</v>
@@ -607,25 +633,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>1111</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -634,25 +660,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2">
         <v>1111</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
@@ -661,25 +687,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2">
         <v>1111</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>11</v>
@@ -688,25 +714,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>1111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>11</v>
@@ -715,25 +741,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
         <v>1111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>11</v>
@@ -742,32 +768,33 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2">
         <v>1234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>